--- a/doc/project_backlog_effort_ja.xlsx
+++ b/doc/project_backlog_effort_ja.xlsx
@@ -12,12 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1名の日程" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3名の予算" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対照" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積根拠" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story工数'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1名の日程'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3名の予算'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'対照'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'見積根拠'!$A$1:$C$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,11 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +57,18 @@
       <name val="Calibri"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +80,13 @@
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,11 +108,25 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFCBD9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFCBD9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFCBD9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFCBD9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,8 +138,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,6 +643,18 @@
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>見積人日 = 人数 × イテレーション数 × 10。管理は責任者だけに掛け、全員には掛けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>第 8 節およびシート「見積根拠」。人日は変えていない。</t>
         </is>
       </c>
     </row>
@@ -609,13 +669,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -639,6 +700,11 @@
           <t>人日</t>
         </is>
       </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -659,6 +725,11 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>受け入れ仮定を 1 枚書く。製品コードはない。書くことと読み返すことで理想時間 1 日。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -679,6 +750,11 @@
       <c r="D3" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>既にあるフレームへ失敗する試験を足す。C と Pascal の二系統。ベクトル、失敗の確認、アサーションで 3 日。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -699,6 +775,11 @@
       <c r="D4" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>セルフホストランナーを登録し、ファームウェア作業が緑になるところまで。makefile の絶対パスという既知の失敗があるため、登録だけでは 1 日にならない。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -719,6 +800,11 @@
       <c r="D5" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>二つのプロジェクトを周辺機能ごとに移し、振舞いを保ったまま Debug と Release をビルドする。再構築であり新機能ではない。理想時間 5 日。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -739,6 +825,11 @@
       <c r="D6" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>システム試験の環境 3.0 人日に、P1 実機 70 時間（8.75 人日）を足すと 11.75。整数の story として 12。P2、長時間、再試験の 3 人日は入れない。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -759,6 +850,11 @@
       <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>RX の比較レジスタ四路だけを直し、波形を確認する。RA は変えない。失敗する試験と実測を含む。システム試験の PWM 波形だけでも 8 時間の規模がある。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -779,6 +875,11 @@
       <c r="D8" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>この系列の最初のコマンド。proto、C、Pascal の基準バイトと二つの基板を触る。5 日は、後続が再利用する型を作る分。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -799,6 +900,11 @@
       <c r="D9" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>型は E2-S1 にある。ここではアドレスと 1 バイトを足し、不正アドレスの失敗を先に置く。最初の八割として 4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -819,6 +925,11 @@
       <c r="D10" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>同じく後続。デモはすでに Break と 0x55 を出す。ホストが渡したバイトへ変える。4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -839,6 +950,11 @@
       <c r="D11" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>三つのコマンドを、一回の画面修正と一組の基準ベクトルにまとめる。プロトコルの手間を三度払わない。3 日。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -859,6 +975,11 @@
       <c r="D12" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>送信経路はある。増えるのは受信メールボックス、CanLog、アナライザでの実機。新しいハードウェア経路として 8 日。RA と折半しない。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -879,6 +1000,11 @@
       <c r="D13" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>受信経路のあとでフィルタを行う。通過と拒否の二つのベクトルと、両側の実装。新しい受信経路より少ない 5 日。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -899,6 +1025,11 @@
       <c r="D14" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>CAN FD のメールボックスはクラシック CAN と同じレジスタではない。RX の 8 日は流用できない。RA でさらに 8 日。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -919,6 +1050,11 @@
       <c r="D15" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>リングは先にホストで同じベクトルを通し、ファームウェアはそれを呼ぶ。256 フレーム、最古を上書き、電源断で消える。Flash を作らないので記憶ドライバの工数ではない。6 日。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -939,6 +1075,11 @@
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>送受信の経路はある。フレームをバッファへ入れ、未接続では送らない。統合として 3 日。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -959,6 +1100,11 @@
       <c r="D17" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ページと消去は新しい符号化である。基準バイトを先に失敗させ、その後通す。基板側の格納は E4-S3。ここは 5 日。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -979,6 +1125,11 @@
       <c r="D18" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>現状は USB クロックと D+ のプルアップだけである。8 日は、同じ HL1 バイトを運ぶデバイス側のパイプまで。USB 認証も高スループットも含まない。パーサは E0-S2 を再利用する。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -999,6 +1150,11 @@
       <c r="D19" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>RA の USB コントローラは RX と異なる。さらに 8 日。UART を受け入れ経路に残すので、この 8 日が失敗しても計画全体は止めない。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1019,6 +1175,11 @@
       <c r="D20" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>フレーム形式は変えない。符号化の試験は元の一式。COM と CDC の選択だけを足す。4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1039,6 +1200,11 @@
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PHY アドレス、アドレスファミリ、ポートは顧客未確認。後続の試験が参照するインタフェース説明を 1 枚。1 日であり、プロトコルスタックではない。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1059,6 +1225,11 @@
       <c r="D22" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAC アドレスと送受信イネーブルは書いてある。10 日は、静的アドレス上の周期 UDP 状態パケット一つまで。TCP、Web、TLS はない。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1079,6 +1250,11 @@
       <c r="D23" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>バイト配置は RX の試験を再利用する。メッセージをゼロから設計し直さない。RGMII と PHY は未確認なので RX より 2 日多く、合計 12 日。PHY が未準備ならバイト試験で止め、リリース日は動かさない。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1099,6 +1275,11 @@
       <c r="D24" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>録音した UDP パケットで画面を動かす。HL1 のコマンド経路は置き換えない。CDC の選択と同じ規模で 4 日。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1119,6 +1300,11 @@
       <c r="D25" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>各 story は自分の実機受け入れをすでに含む。ここはリリース前にもう一度既存 P1 を行い、新しいコマンドを抜き取る。やはり 12 日。現行試験の 18.5 人日を重ねては足さない。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1138,6 +1324,11 @@
       </c>
       <c r="D26" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>日中の文書の本体はすでにリポジトリにある。3 日は、動作の変化を反映し、タグを打ち、リリース成果物を確認する分。仕様をゼロから書く日数ではない。</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2314,10 +2505,10 @@
           <t>終了日</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="8" t="n">
         <v>46661</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="8" t="n">
         <v>46437</v>
       </c>
     </row>
@@ -2413,4 +2604,416 @@
   <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>数字</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>E0-S1 最可能 1</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>O 0.8，P 1.5，期望 1.0。受け入れ仮定を 1 枚書く。製品コードはない。書くことと読み返すことで理想時間 1 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>E0-S2 最可能 3</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。既にあるフレームへ失敗する試験を足す。C と Pascal の二系統。ベクトル、失敗の確認、アサーションで 3 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>E0-S4 最可能 2</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>O 1.4，P 3.6，期望 2.2。セルフホストランナーを登録し、ファームウェア作業が緑になるところまで。makefile の絶対パスという既知の失敗があるため、登録だけでは 1 日にならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>E0-S5 最可能 5</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>O 3.8，P 7.5，期望 5.2。二つのプロジェクトを周辺機能ごとに移し、振舞いを保ったまま Debug と Release をビルドする。再構築であり新機能ではない。理想時間 5 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>E0-S3 最可能 12</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>O 8.4，P 21.6，期望 13.0。システム試験の環境 3.0 人日に、P1 実機 70 時間（8.75 人日）を足すと 11.75。整数の story として 12。P2、長時間、再試験の 3 人日は入れない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>E1-S1 最可能 3</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>O 2.1，P 5.4，期望 3.2。RX の比較レジスタ四路だけを直し、波形を確認する。RA は変えない。失敗する試験と実測を含む。システム試験の PWM 波形だけでも 8 時間の規模がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>E2-S1 最可能 5</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。この系列の最初のコマンド。proto、C、Pascal の基準バイトと二つの基板を触る。5 日は、後続が再利用する型を作る分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>E2-S2 最可能 4</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。型は E2-S1 にある。ここではアドレスと 1 バイトを足し、不正アドレスの失敗を先に置く。最初の八割として 4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>E2-S3 最可能 4</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。同じく後続。デモはすでに Break と 0x55 を出す。ホストが渡したバイトへ変える。4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>E2-S4 最可能 3</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。三つのコマンドを、一回の画面修正と一組の基準ベクトルにまとめる。プロトコルの手間を三度払わない。3 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>E3-S1 最可能 8</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。送信経路はある。増えるのは受信メールボックス、CanLog、アナライザでの実機。新しいハードウェア経路として 8 日。RA と折半しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>E3-S2 最可能 8</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。CAN FD のメールボックスはクラシック CAN と同じレジスタではない。RX の 8 日は流用できない。RA でさらに 8 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>E3-S3 最可能 5</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。受信経路のあとでフィルタを行う。通過と拒否の二つのベクトルと、両側の実装。新しい受信経路より少ない 5 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>E4-S1 最可能 6</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>O 4.2，P 10.8，期望 6.5。リングは先にホストで同じベクトルを通し、ファームウェアはそれを呼ぶ。256 フレーム、最古を上書き、電源断で消える。Flash を作らないので記憶ドライバの工数ではない。6 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>E4-S2 最可能 5</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>O 3.5，P 9.0，期望 5.4。ページと消去は新しい符号化である。基準バイトを先に失敗させ、その後通す。基板側の格納は E4-S3。ここは 5 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>E4-S3 最可能 3</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。送受信の経路はある。フレームをバッファへ入れ、未接続では送らない。統合として 3 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>E5-S1 最可能 8</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。現状は USB クロックと D+ のプルアップだけである。8 日は、同じ HL1 バイトを運ぶデバイス側のパイプまで。USB 認証も高スループットも含まない。パーサは E0-S2 を再利用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>E5-S2 最可能 8</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>O 4.8，P 17.6，期望 9.1。RA の USB コントローラは RX と異なる。さらに 8 日。UART を受け入れ経路に残すので、この 8 日が失敗しても計画全体は止めない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>E5-S3 最可能 4</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。フレーム形式は変えない。符号化の試験は元の一式。COM と CDC の選択だけを足す。4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>E6-S1 最可能 1</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>O 0.8，P 1.5，期望 1.0。PHY アドレス、アドレスファミリ、ポートは顧客未確認。後続の試験が参照するインタフェース説明を 1 枚。1 日であり、プロトコルスタックではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>E6-S2 最可能 10</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>O 6.0，P 22.0，期望 11.3。MAC アドレスと送受信イネーブルは書いてある。10 日は、静的アドレス上の周期 UDP 状態パケット一つまで。TCP、Web、TLS はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>E6-S3 最可能 12</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>O 7.2，P 26.4，期望 13.6。バイト配置は RX の試験を再利用する。メッセージをゼロから設計し直さない。RGMII と PHY は未確認なので RX より 2 日多く、合計 12 日。PHY が未準備ならバイト試験で止め、リリース日は動かさない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>E6-S4 最可能 4</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>O 3.0，P 6.0，期望 4.2。録音した UDP パケットで画面を動かす。HL1 のコマンド経路は置き換えない。CDC の選択と同じ規模で 4 日。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>E7-S1 最可能 12</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>O 8.4，P 21.6，期望 13.0。各 story は自分の実機受け入れをすでに含む。ここはリリース前にもう一度既存 P1 を行い、新しいコマンドを抜き取る。やはり 12 日。現行試験の 18.5 人日を重ねては足さない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>E7-S2 最可能 3</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>O 2.2，P 4.5，期望 3.1。日中の文書の本体はすでにリポジトリにある。3 日は、動作の変化を反映し、タグを打ち、リリース成果物を確認する分。仕様をゼロから書く日数ではない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>